--- a/SGC-CKN/Excel/6c2552a4-4729-4c6e-aed4-6d82875630d0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-26_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/6c2552a4-4729-4c6e-aed4-6d82875630d0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P11-26_D800_20-03-2026.xlsx
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">06:10
@@ -108,7 +108,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">06:20
@@ -121,7 +121,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">07:50
@@ -134,7 +134,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sét-đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:40
@@ -147,7 +147,7 @@
     <t>11</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng, xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">08:50
@@ -173,7 +173,7 @@
     <t>13</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -186,7 +186,7 @@
     <t>14</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:01
@@ -199,7 +199,7 @@
     <t>16</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13:46
